--- a/data_example/data_peserta.xlsx
+++ b/data_example/data_peserta.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ariefsetyonugroho/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ariefsetyonugroho/Documents/Website/funRun/data_example/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7F076EE9-2703-BD4A-9F59-F94F3B9C23E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{029843FD-08A4-094D-962D-F765BFFD773C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="43040" yWindow="2540" windowWidth="28040" windowHeight="17260" xr2:uid="{2399FBA6-FA85-0E4A-A61B-57645AA3B817}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" xr2:uid="{2399FBA6-FA85-0E4A-A61B-57645AA3B817}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t>id</t>
   </si>
@@ -50,6 +50,12 @@
   </si>
   <si>
     <t>Alam Budi Kusuma</t>
+  </si>
+  <si>
+    <t>A2527</t>
+  </si>
+  <si>
+    <t>Rehan</t>
   </si>
 </sst>
 </file>
@@ -401,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{087F7510-4A16-B843-9E8C-C0E637D118B1}">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="21.6640625" customWidth="1"/>
@@ -441,6 +447,17 @@
         <v>4</v>
       </c>
     </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
